--- a/data/trans_orig/IP22-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP22-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>81354</t>
+          <t>81221</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93368</t>
+          <t>92910</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>68638</t>
+          <t>68621</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81897</t>
+          <t>81723</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>153587</t>
+          <t>153853</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>172020</t>
+          <t>171118</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,75%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>4411</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>10842</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22249</t>
+          <t>22658</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14633</t>
+          <t>14373</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27479</t>
+          <t>27233</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27963</t>
+          <t>28505</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>46156</t>
+          <t>45129</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57601</t>
+          <t>58643</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>70920</t>
+          <t>71175</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58208</t>
+          <t>58002</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>71154</t>
+          <t>71233</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>120643</t>
+          <t>120677</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>139182</t>
+          <t>138476</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>79,88%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16469</t>
+          <t>16214</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29788</t>
+          <t>28746</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14374</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27037</t>
+          <t>27349</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33260</t>
+          <t>34466</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51696</t>
+          <t>52641</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,37%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45128</t>
+          <t>45606</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56469</t>
+          <t>56683</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>68114</t>
+          <t>68487</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>82583</t>
+          <t>81960</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>118291</t>
+          <t>118289</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>135593</t>
+          <t>135368</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,19%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10923</t>
+          <t>10709</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22264</t>
+          <t>21786</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16749</t>
+          <t>17372</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31218</t>
+          <t>30845</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31131</t>
+          <t>31356</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48433</t>
+          <t>48435</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>148830</t>
+          <t>148962</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>167535</t>
+          <t>167399</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>146458</t>
+          <t>147135</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>166102</t>
+          <t>165935</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>302873</t>
+          <t>302751</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>329410</t>
+          <t>328354</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,52%</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>3410</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4712</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32331</t>
+          <t>32776</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50867</t>
+          <t>50693</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35513</t>
+          <t>35471</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54952</t>
+          <t>54140</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>72229</t>
+          <t>73041</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>98555</t>
+          <t>98860</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>81741</t>
+          <t>82100</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>93865</t>
+          <t>94032</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>93824</t>
+          <t>93561</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>108378</t>
+          <t>107992</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>178757</t>
+          <t>179802</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>198037</t>
+          <t>198523</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,79%</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>10088</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22379</t>
+          <t>22020</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18230</t>
+          <t>18661</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32557</t>
+          <t>32757</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>31856</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51949</t>
+          <t>50255</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>52456</t>
+          <t>52682</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>64430</t>
+          <t>64603</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>53384</t>
+          <t>53683</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>64365</t>
+          <t>64263</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>109861</t>
+          <t>110248</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>125595</t>
+          <t>126430</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,85%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10440</t>
+          <t>10267</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22414</t>
+          <t>22188</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19008</t>
+          <t>18709</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21667</t>
+          <t>20832</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>37401</t>
+          <t>37014</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>495764</t>
+          <t>492706</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>527648</t>
+          <t>527446</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>516548</t>
+          <t>516718</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>551708</t>
+          <t>549769</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1020173</t>
+          <t>1019085</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1068461</t>
+          <t>1066794</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,61%</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9086</t>
+          <t>9074</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>109755</t>
+          <t>109953</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>142187</t>
+          <t>143872</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>130631</t>
+          <t>131407</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>164039</t>
+          <t>164574</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>250523</t>
+          <t>252266</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>297802</t>
+          <t>299230</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61042</t>
+          <t>60906</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74384</t>
+          <t>73662</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60758</t>
+          <t>59744</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74377</t>
+          <t>74040</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>126278</t>
+          <t>125635</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144665</t>
+          <t>144957</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,67%</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3111</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15116</t>
+          <t>15536</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28076</t>
+          <t>28129</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15386</t>
+          <t>15723</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29005</t>
+          <t>30019</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34774</t>
+          <t>34391</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52848</t>
+          <t>53202</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62509</t>
+          <t>62640</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76086</t>
+          <t>76314</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61211</t>
+          <t>61270</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76160</t>
+          <t>76096</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>127401</t>
+          <t>127971</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>147875</t>
+          <t>147992</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,18%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>717</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6832</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>693</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7070</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>2282</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10089</t>
+          <t>10800</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14541</t>
+          <t>14091</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27682</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18026</t>
+          <t>18138</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31747</t>
+          <t>32738</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35734</t>
+          <t>36250</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56066</t>
+          <t>55779</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62131</t>
+          <t>62264</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74000</t>
+          <t>74487</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>60068</t>
+          <t>59072</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72825</t>
+          <t>72665</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>126380</t>
+          <t>126452</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>144137</t>
+          <t>144043</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,24%</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11266</t>
+          <t>10836</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23026</t>
+          <t>23137</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14065</t>
+          <t>14225</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26822</t>
+          <t>27818</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28404</t>
+          <t>28129</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46409</t>
+          <t>45395</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>137042</t>
+          <t>136719</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>158174</t>
+          <t>157832</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>148888</t>
+          <t>149641</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>171282</t>
+          <t>171846</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>290677</t>
+          <t>292079</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>321804</t>
+          <t>323578</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,64%</t>
         </is>
       </c>
     </row>
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>571</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>571</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47934</t>
+          <t>48276</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69066</t>
+          <t>69389</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>54372</t>
+          <t>54029</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>76022</t>
+          <t>76073</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>109353</t>
+          <t>108270</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>140443</t>
+          <t>139165</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,1%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>109940</t>
+          <t>109467</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>126253</t>
+          <t>126020</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>87295</t>
+          <t>86670</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>106336</t>
+          <t>105137</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>202218</t>
+          <t>201939</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>228076</t>
+          <t>227576</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,65%</t>
         </is>
       </c>
     </row>
@@ -6136,7 +6136,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5038</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22916</t>
+          <t>23149</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39229</t>
+          <t>39702</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32561</t>
+          <t>33172</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51523</t>
+          <t>51561</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59892</t>
+          <t>60484</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85743</t>
+          <t>86160</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,78%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>41168</t>
+          <t>41227</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>50284</t>
+          <t>50314</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>50041</t>
+          <t>50045</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>62052</t>
+          <t>62495</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>95389</t>
+          <t>94546</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>109904</t>
+          <t>109779</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,8%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>12684</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11986</t>
+          <t>11543</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23997</t>
+          <t>23993</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>18045</t>
+          <t>18170</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32560</t>
+          <t>33403</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>499647</t>
+          <t>501066</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>537903</t>
+          <t>537655</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>498137</t>
+          <t>496935</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>537377</t>
+          <t>538185</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1008980</t>
+          <t>1009800</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1063045</t>
+          <t>1062933</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,31%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8303</t>
+          <t>8416</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10647</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>16708</t>
+          <t>16277</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>135850</t>
+          <t>137618</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>174264</t>
+          <t>172979</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>171633</t>
+          <t>169872</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>211265</t>
+          <t>210588</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>320681</t>
+          <t>320385</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>372887</t>
+          <t>373890</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60298</t>
+          <t>60128</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72049</t>
+          <t>71606</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>72935</t>
+          <t>72462</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86466</t>
+          <t>85405</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>137453</t>
+          <t>138154</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>154529</t>
+          <t>154864</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>85,06%</t>
         </is>
       </c>
     </row>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>760</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6563</t>
+          <t>6988</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10501</t>
+          <t>10840</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22112</t>
+          <t>22037</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10828</t>
+          <t>11485</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23429</t>
+          <t>23511</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25442</t>
+          <t>24819</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42231</t>
+          <t>40986</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80613</t>
+          <t>79228</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92875</t>
+          <t>92597</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88047</t>
+          <t>87892</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>100270</t>
+          <t>100444</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>172579</t>
+          <t>172129</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>190525</t>
+          <t>190008</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>86,98%</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11683</t>
+          <t>12077</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23591</t>
+          <t>24828</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12476</t>
+          <t>12302</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24699</t>
+          <t>24854</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26608</t>
+          <t>26924</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44210</t>
+          <t>44676</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48709</t>
+          <t>48172</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56940</t>
+          <t>57140</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55369</t>
+          <t>54348</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65978</t>
+          <t>65869</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>107035</t>
+          <t>106998</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120661</t>
+          <t>121164</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,27%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13131</t>
+          <t>13668</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9450</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20059</t>
+          <t>21080</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16607</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30233</t>
+          <t>30270</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>170216</t>
+          <t>169711</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>189545</t>
+          <t>188392</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>165636</t>
+          <t>166530</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>183382</t>
+          <t>184747</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>341386</t>
+          <t>341813</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>366748</t>
+          <t>368474</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,82%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>697</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>663</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6995</t>
+          <t>6641</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31987</t>
+          <t>32591</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50778</t>
+          <t>51258</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27472</t>
+          <t>26107</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45218</t>
+          <t>44324</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>64314</t>
+          <t>63689</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>90336</t>
+          <t>88414</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,35%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>102628</t>
+          <t>102672</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>117288</t>
+          <t>116876</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>108167</t>
+          <t>109686</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>124700</t>
+          <t>125114</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>216817</t>
+          <t>216120</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>237518</t>
+          <t>237720</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,12%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>7879</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16967</t>
+          <t>17595</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30804</t>
+          <t>31324</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17148</t>
+          <t>16646</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34137</t>
+          <t>32212</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38550</t>
+          <t>38438</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58809</t>
+          <t>59440</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>49977</t>
+          <t>49626</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>58204</t>
+          <t>57859</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>53097</t>
+          <t>52630</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>62652</t>
+          <t>62698</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>106485</t>
+          <t>106540</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>118792</t>
+          <t>118876</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,22%</t>
         </is>
       </c>
     </row>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3731</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9998,7 +9998,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -10091,12 +10091,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10106,12 +10106,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14728</t>
+          <t>15195</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9528</t>
+          <t>9478</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>21564</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>537384</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>567121</t>
+          <t>568066</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>569743</t>
+          <t>569230</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>603307</t>
+          <t>604766</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1115844</t>
+          <t>1119231</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1161395</t>
+          <t>1165028</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,4%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>4144</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13241</t>
+          <t>13359</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>7696</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>6496</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>17951</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>97504</t>
+          <t>96682</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>127981</t>
+          <t>127447</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>102876</t>
+          <t>101525</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>136459</t>
+          <t>135387</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>207080</t>
+          <t>204853</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>252114</t>
+          <t>251169</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,2%</t>
         </is>
       </c>
     </row>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76328</t>
+          <t>75926</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88961</t>
+          <t>88971</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>108807</t>
+          <t>108725</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>123122</t>
+          <t>123128</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>188169</t>
+          <t>188520</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>208436</t>
+          <t>209092</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,63%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>15491</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28134</t>
+          <t>28536</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13786</t>
+          <t>13780</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28101</t>
+          <t>28183</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32934</t>
+          <t>32278</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53201</t>
+          <t>52850</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>76922</t>
+          <t>77157</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87210</t>
+          <t>87012</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>73440</t>
+          <t>74612</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>86738</t>
+          <t>86896</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,47 +11517,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>90,92%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>164456</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>154829</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>172021</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>86,77%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>81,69%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>90,76%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>164456</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>155068</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>171965</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>86,77%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>81,82%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>90,73%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6946</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17036</t>
+          <t>16801</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>8677</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22133</t>
+          <t>20961</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,47 +11743,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>9,08%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>21,93%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>25075</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>17510</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>34702</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>13,23%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>9,24%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>23,16%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>25075</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>17566</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>34463</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>13,23%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39011</t>
+          <t>39512</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47455</t>
+          <t>48040</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42471</t>
+          <t>43055</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55298</t>
+          <t>55318</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>85335</t>
+          <t>84696</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>101469</t>
+          <t>101005</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,29%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12850</t>
+          <t>12349</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8555</t>
+          <t>8535</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21382</t>
+          <t>20798</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14245</t>
+          <t>14709</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30379</t>
+          <t>31018</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>164675</t>
+          <t>162714</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>195318</t>
+          <t>193940</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>169729</t>
+          <t>169836</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>190833</t>
+          <t>190785</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>343189</t>
+          <t>341403</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>381224</t>
+          <t>380135</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,13%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22692</t>
+          <t>24070</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53335</t>
+          <t>55296</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27439</t>
+          <t>27487</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48543</t>
+          <t>48436</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>55058</t>
+          <t>56147</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>93093</t>
+          <t>94879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>93021</t>
+          <t>92988</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>105633</t>
+          <t>106232</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>126847</t>
+          <t>127908</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>146351</t>
+          <t>146511</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>226531</t>
+          <t>225837</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>249313</t>
+          <t>249352</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,41%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13795</t>
+          <t>13196</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26407</t>
+          <t>26440</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16266</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35770</t>
+          <t>34709</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32732</t>
+          <t>32693</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55514</t>
+          <t>56208</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>57336</t>
+          <t>56754</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>66257</t>
+          <t>65920</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>60359</t>
+          <t>60882</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>69318</t>
+          <t>69115</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>121645</t>
+          <t>121457</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>133975</t>
+          <t>133731</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11559</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11644</t>
+          <t>11121</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6923</t>
+          <t>7167</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19253</t>
+          <t>19441</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>532792</t>
+          <t>531390</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>573272</t>
+          <t>571490</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>613583</t>
+          <t>614766</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>652159</t>
+          <t>652895</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1158203</t>
+          <t>1160682</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1215811</t>
+          <t>1214473</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,39%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>83342</t>
+          <t>85124</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>123822</t>
+          <t>125224</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>97066</t>
+          <t>96330</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>135642</t>
+          <t>134459</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>190028</t>
+          <t>191366</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>247636</t>
+          <t>245157</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
